--- a/frontend/public/catalog-import-template.xlsx
+++ b/frontend/public/catalog-import-template.xlsx
@@ -65,7 +65,7 @@
     <t>Иванова Анна (пример)</t>
   </si>
   <si>
-    <t>Петров Пётр (пример), проректор</t>
+    <t>Петров Пётр (пример)</t>
   </si>
   <si>
     <t>Лицензия передана, запланировано обучение</t>
